--- a/docs/deliverables/PRESS-CMS_통합현황표.xlsx
+++ b/docs/deliverables/PRESS-CMS_통합현황표.xlsx
@@ -48,7 +48,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">기능 현황 + 작업지시서 요구사항 매핑 · 2026-10-16 기준 · 첨부표(42개 기능)에 이후 작업과 10-14 로컬 시험 결과를 반영</t>
+    <t xml:space="preserve">기능 현황 + 작업지시서 요구사항 매핑 · 2026-10-19 기준 · 첨부표(42개 기능)에 이후 작업과 10-14~10-19 시험 결과를 반영</t>
   </si>
   <si>
     <t xml:space="preserve">상태</t>
@@ -594,6 +594,1182 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">(10-19): </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">통과 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">42</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">건 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">실패 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">T41(OpenAI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">화자 구분 모델의 한국어 한계</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">보류 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">T24·T42·T43·T46·T47</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">• 확인 필요 칸의 옛 문구("이번 작업 범위 아님", 상태·비고 불일치 등) 중 이미 해결된 것은 지움</t>
+  </si>
+  <si>
+    <t xml:space="preserve">사용 방법</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. [</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">통합 현황표</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">시트의 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">열</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">현재 상태</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">은 목록에서 고릅니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">바꾸면 이 시트의 개수가 자동으로 바뀝니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">노란색 칸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">확인 필요 사항</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">은 사람이 직접 확인해야 하는 내용입니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">확인 후 상태를 갱신해 주세요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3. "🧪 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">구현</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">시험전</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">은 첨부표의 범례에 없던 새 표시입니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">코드를 완성했지만 실제 서비스에서 시험하지 않았다는 뜻입니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4. [</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">작업지시서 매핑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">시트는 동아일보 부트캠프 작업지시서의 필수 기능</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">핵심 기술</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">제약사항</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">산출물이 통합표의 어느 항목에 해당하는지 보여 줍니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">번호</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기능</t>
+  </si>
+  <si>
+    <t xml:space="preserve">작업지시서 매핑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">첨부표 상태(이전)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">현재 상태</t>
+  </si>
+  <si>
+    <t xml:space="preserve">현재 상황 / 비고</t>
+  </si>
+  <si>
+    <t xml:space="preserve">확인 필요 사항</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기사 작성</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">편집 코어</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기사 작성·편집</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✅</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제목·부제목·본문 작성·저장</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">연속형 본문 편집기</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🟡</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화면 확인(2026-10-08): 제목·부제목·분류·본문이 한 장의 흰 문서 안에 이어서 보임</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">본문 미디어 삽입</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이미지 캡션·크레딧·자르기, 본문 사이 끌어놓기 삽입이 코드에 있음</t>
+  </si>
+  <si>
+    <t xml:space="preserve">사진이 들어간 기사로 한 번 눈으로 확인 권장.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미디어 드래그 앤 드롭</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🔴</t>
+  </si>
+  <si>
+    <t xml:space="preserve">사진을 끌어다 놓는 처리(드래그 앤 드롭)가 코드에 다시 들어 있음 (BodyEditor)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화면에서 직접 끌어 놓아 보는 시험은 아직 안 했습니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기사 자동저장</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">article_blocks </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기반</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">워크플로우</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">출고</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">권한</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기사 상태 관리</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">🔴(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">오류발생</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">검토 요청 · 수정 요청 · 승인 · 출고 단계가 서버 기능으로 모두 있고, 편집기에서 상태를 바꿀 수 있음. 해결되었다는 보고 반영</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"오류발생" 원인은 표에 적혀 있지 않아, 해결 여부는 화면 시험으로 한 번 더 확인 권장.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">출고대기 자동 노출</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">출고 대기 기사는 공유 설정과 무관하게 부장 이상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">부장 직급 또는 편집국장 역할</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">의 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">출고 대기 검토</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">에만 표시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(10-12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">팀 결정으로 범위를 좁힘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">10-16 사용자가 차장 계정으로 "출고 대기 검토"가 보이지 않음을 확인. 제한은 화면 목록 기준(서버 규칙은 그대로).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기사 공유 범위 설정</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미공개/같은 부서/전체</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공유와 출고검토 분리</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미공개라도 출고 대기면 부장 이상이 검토 가능</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">부서 기반 데스크 검토</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">🟡(↑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개선</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">서버가 같은 부서 데스크만 수정요청</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">승인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배정을 허용</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">규칙을 문서로 정리함 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(docs/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">부서별</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">권한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">정책</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.md)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">다른 부서 대리 승인, 차장 최종 출고, 편집국장 전체 열람 여부는 팀이 정해야 함. 출고 대기 검토는 10-12부터 부장 이상만 보임(7번).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">사용자·직급별 권한</t>
+  </si>
+  <si>
+    <t xml:space="preserve">수습·평기자·차장·부장 구조</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">최종 출고 권한</t>
+  </si>
+  <si>
+    <t xml:space="preserve">부장 권한 기준</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C. AI </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">검수</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(Review) — </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기존 구현</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">13</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기사 검수</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">review-article-content. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이제 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Gemini</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">뿐 아니라 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">OpenAI·Claude·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">사내 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">API </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">중 내가 고른 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로 동작 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10-12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">검수 지침 보강</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">: </t>
     </r>
     <r>
@@ -602,143 +1778,649 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">통과 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">41</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">건 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">실패 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">T41(OpenAI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">화자 구분 모델의 한국어 한계</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">) / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">보류 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">T20·T24·T42·T43·T46·T47</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">• 확인 필요 칸의 옛 문구("이번 작업 범위 아님", 상태·비고 불일치 등) 중 이미 해결된 것은 지움</t>
-  </si>
-  <si>
-    <t xml:space="preserve">사용 방법</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1. [</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">통합 현황표</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">시트의 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">E</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">열</t>
+      <t xml:space="preserve">주어 누락</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">제목에만 있는 내용</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">영문 표기 한글 우선</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">해외 대학</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기관 앞 국가명</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">보강분은 서버 함수 재배포 후 예문 시험 전. 공급자별 실사용도 시험 전(Gemini는 사용 확인됨).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">비문 검수</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">주술호응·성분누락·조사·시제 등 (10-12 주어 누락 지적 보강)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">검수 상세 설명</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">원문·유형·이유·확인사항·수정예시</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제목-본문 정합성 검사</t>
+  </si>
+  <si>
+    <t xml:space="preserve">인물·기관·수치·주장 불일치 검수 (10-12 제목에만 있는 내용 지적 보강)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기사 표기법 검수</t>
+  </si>
+  <si>
+    <t xml:space="preserve">외래어·숫자·날짜·단위 등 (10-12 영문 표기 한글 우선·해외 기관 앞 국가명 규칙 추가)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PRESS-CMS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기사 가이드</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">별도 문서 완비(표기 가이드 v1.1: 10-12 해외 대학·기관 앞 국가명 항목 추가)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원문 자동수정 방지</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">임의 원문 변경 금지 원칙 유지</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D. AI </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">초안 생성 — 작업지시서 대응</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">D-1</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기사 초안 작성</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">작업지시서 ①</t>
+  </si>
+  <si>
+    <t xml:space="preserve">질문형 인터뷰(AI Interview Draft): ai-interview-draft + AiInterviewDraftPanel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">로우데이터 요약·정리</t>
+  </si>
+  <si>
+    <t xml:space="preserve">작업지시서 ②</t>
+  </si>
+  <si>
+    <t xml:space="preserve">취재메모/보도자료 → 5W1H·인용구·수치 구조화. 이번에 TXT·CSV·MD 파일 불러오기, 정리 전으로 되돌리기, 원자료에 없는 발언·숫자 걸러내기 추가</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10-16 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로컬 시험 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">T07~T15 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">모두 통과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(gemini-3.5-flash-lite): </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">숫자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">발언 원문 그대로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">문서 속 지시문 무시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">엇갈린 숫자 확인 필요로 분리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">한글 엑셀 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CSV </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">읽기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만 자 초과 안내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">D-3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">대화형(Chat) 프롬프트</t>
+  </si>
+  <si>
+    <t xml:space="preserve">작업지시서 ③</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">질문</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기자 답변 채팅 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">UI</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">D-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">피드백→재생성 루프</t>
+  </si>
+  <si>
+    <t xml:space="preserve">작업지시서 ④</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">regenerate_section </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">모드로 섹션별 재작성 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전체 수정 지시</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">T16~T19·T21 통과. T19는 10-16 문단 순서가 바뀌는 오류를 고친 뒤 재시험 통과(고른 문단만 바뀌고 리드·다른 문단 그대로). 별점·점수 기록은 만들지 않기로 결정(N-10).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">제목 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개 추천</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">✅(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">통합</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">독립 기능 대신 인터뷰 finalize 결과에 제목 후보 2~3개로 통합 구현 (통합 구현)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">톤·스타일·키워드 기반 작성</t>
+  </si>
+  <si>
+    <t xml:space="preserve">작업지시서 핵심기술(프롬프트)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기사 어조 선택(스트레이트/해설·분석/인터뷰/피처)이 화면에 있고 서버가 어조별 지시문을 적용함</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10-16 T03 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">통과</t>
     </r>
     <r>
       <rPr>
@@ -755,7 +2437,272 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">현재 상태</t>
+      <t xml:space="preserve">해설 톤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배경</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">맥락이 늘고 사실 동일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">). </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인터뷰 톤으로 다시 만들기는 화면 변화가 확인되지 않음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">D-6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">본문 반영 안전성</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI 초안 [본문 삽입]은 편집기에 직접 넣고 바로 저장(10-14 본문에 안 들어가던 오류 수정, 로컬 확인). 직접 INSERT 미사용</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D-7</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">모델 라우팅 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">번째 슬롯</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ai_system_settings.article_generation_model(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">팀 기본값</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">). 10-16</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">부터 실제 호출은 사람마다 저장한 기능별 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI(N-23)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">를 따름</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">SQL 20261014100000 실행 완료.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">E. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">협업 피드백</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">드래그형 기사 피드백</t>
+  </si>
+  <si>
+    <t xml:space="preserve">본문 글자를 드래그해 선택하면 피드백 입력창이 열리고 선택한 문장이 함께 저장됨 (코드 확인)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">피드백 형광펜 표시</t>
+  </si>
+  <si>
+    <t xml:space="preserve">피드백이 달린 문장을 형광펜으로 표시 (feedbackHighlight)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">피드백 위치 바로가기</t>
+  </si>
+  <si>
+    <t xml:space="preserve">피드백을 누르면 본문의 해당 위치로 부드럽게 이동. 위치를 못 찾으면 "원문 위치를 찾을 수 없음" 표시</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">피드백 위치 복구</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🔵</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">본문이 조금 바뀌어도 앞뒤 문맥과 선택 문장으로 위치를 다시 찾는 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">단계 복구가 들어 있음 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(DB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">에도 문맥 칸 추가</t>
     </r>
     <r>
       <rPr>
@@ -766,13 +2713,948 @@
       </rPr>
       <t xml:space="preserve">)</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">은 목록에서 고릅니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">본문을 크게 고친 뒤 실제로 위치가 따라오는지는 시험 전.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이력</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">분류</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기사 분류</t>
+  </si>
+  <si>
+    <t xml:space="preserve">정치·경제·사회 등</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">해시태그</t>
+  </si>
+  <si>
+    <t xml:space="preserve">추가·삭제 UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기사 이력 관리</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">History </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">영역</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">G. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">조직</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/HR</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">28</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HR </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">프로필 설정 복구</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">인사 담당자는 환경설정에서 AI·미디어 메뉴를 빼고 내 프로필만 보이게 정리. 라벨도 인사 관리자용으로 변경</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HR 계정으로 로그인해 확인 필요. 10-14 인사부 전용 왼쪽 메뉴와 사용법 안내 버튼 추가(N-19).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HR </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">직원 명부</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">보안 RPC 구현 완료</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HR </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">직원정보 수정</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">직원 명부의 [수정] 버튼: 부서·직책·직급·시스템 역할을 바꿈 (본인 계정은 제외). 바꾸면 변경 기록에 남고 본인에게 알림</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10-16 사용자가 인사부 계정으로 동작 확인.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">직원 계정 비활성화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">직원 명부의 [비활성화]/[다시 사용] 버튼: 로그인 차단 + 접속 중인 세션 종료. 기사·기록은 그대로 보존. 로그인 화면에 "비활성화된 계정입니다" 안내</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10-16 사용자가 인사부 계정으로 동작 확인. 이미 열린 화면은 최대 1시간 안에 끊길 수 있음.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">회원가입 승인 관리</t>
+  </si>
+  <si>
+    <t xml:space="preserve">가입 신청 즉시 승인 대기 계정 생성 + 임시 비밀번호(한 번만 표시). 인사부 승인 시 부서·직책·직급·역할 반영, 반려 시 사용 중지(10-12 변경, N-14·N-15)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10-16 사용자가 새 가입 신청 흐름을 확인.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">H. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">알림</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">감사</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">통합 알림센터</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상단 🔔 알림센터 구현. 모든 화면에서 열람, 읽음·모두 읽음 처리</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HR </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가입승인 알림</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">누가 가입을 신청하면 인사 담당자 전원에게 "가입 승인 요청" 알림. 누르면 가입 승인 메뉴로 이동. 인사 포털 상단에도 🔔 표시</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQL 실행 후 시험 필요.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기사 피드백 알림</t>
+  </si>
+  <si>
+    <t xml:space="preserve">수정 요청 알림 + 새 피드백 알림 구현. 2026-10-08 사용자가 실제 알림 도착 확인</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">출고대기 알림</t>
+  </si>
+  <si>
+    <t xml:space="preserve">검토 요청·재검토 요청·승인 완료·출고 완료 알림 있음</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">인사정보 변경 알림</t>
+  </si>
+  <si>
+    <t xml:space="preserve">인사 담당자가 내 부서·직책·직급·역할 등을 바꾸면 본인에게 "인사 정보 변경" 알림 (바뀐 내용 포함)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">알림 업무 바로가기</t>
+  </si>
+  <si>
+    <t xml:space="preserve">알림을 누르면 해당 기사로 바로 이동</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">알림 영구저장·Realtime</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">알림이 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">에 영구 저장되고 새 알림이 오면 바로 🔔에 반영</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(Realtime). </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">사용자가 정상 동작 확인</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Realtime이 끊겨도 60초마다 다시 확인.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">감사 로그</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기사 감사 기록 8종 + 인사·권한 변경 기록(직원 정보·부서·직책 변경 시 자동 기록, 인사 포털 "인사·권한 변경 기록" 메뉴)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">마이그레이션 20261008210000 실행 후 확인 필요.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상단 헤더 단순화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상단 헤더에 검색·알림센터·내 프로필 중심으로 정리됨 (코드 확인)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화면 모양은 직접 확인 권장.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">I. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인프라 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">작업지시서 전용 항목</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">42</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Supabase </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">데이터 연동</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Auth/Postgres/Storage/Edge Functions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I-1</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">STT(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">음성→텍스트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">핵심기술: 음성 데이터의 텍스트 변환</t>
+  </si>
+  <si>
+    <t xml:space="preserve">구현·실사용 확인(Gemini). [녹음 받아쓰기]: 언어 4개, 발표·강연/인터뷰(화자 구분), 화자 이름 바꾸기, 엔진 3종(Gemini·OpenAI·구글 클라우드). 2026-10-08 합성 음성으로 인터뷰(화자1·2 분리)·발표(화자 표시 없음)·영어(번역 없이 영어 그대로) 모두 통과. Claude는 소리를 들을 수 없어 제외 10-14 받아쓰기 모델을 글쓰기 모델과 따로 고르도록 분리(N-18).</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10-16 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로컬 재시험 통과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(Gemini gemini-3.8-flash·gemini-3.6-flash, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">발표</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인터뷰 모두</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">). 3.8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">은 첫 시도 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회 빈 결과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">("</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">받아 적을 말을 찾지 못했습니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">") </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">후 재시도에서 정상 — 가끔 다시 눌러야 할 수 있음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. gemini-3.5-transcribe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">는 실패해 목록에서 뺌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. OpenAI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">는 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10-16 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">시험</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(N-11 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">참고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">구글 클라우드는 사용자 결정으로 보류</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">조직 정책으로 키 생성이 막힘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">). </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">받아쓴 지명</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">숫자는 반드시 확인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">합성 음성의 시 이름이 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">당진</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"/"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">하나시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로 다르게 적힘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">).</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">I-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이미지 생성 AI API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">핵심기술: 이미지 생성 AI API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">구현됨. 미디어 탭 [AI 이미지]: 설명글→생성→미리보기→라이브러리 업로드. 출처 "AI 생성(모델명)"과 캡션 [AI 생성 이미지] 자동 표기. Gemini·OpenAI 지원</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10-16 OpenAI 키로 시험 통과(T33): gpt-image-2.5-flare로 생성, 올리면 캡션 [AI 생성 이미지]·출처 "AI 생성 (OpenAI gpt-image-2.5-flare)" 자동 표기. T34: 실제 로고가 그려지는 문제를 발견해, 로고·상표·실존 인물 얼굴 요청은 AI 호출 전에 거절하도록 고친 뒤 통과. Gemini 이미지 모델은 결제 연결 키가 없어 시험 못 함. OpenAI 이미지는 요금이 높으니 주의.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I-3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">웹크롤링·데이터 처리</t>
+  </si>
+  <si>
+    <t xml:space="preserve">핵심기술: 웹 크롤링 및 데이터 처리</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🟠</t>
+  </si>
+  <si>
+    <t xml:space="preserve">구현됨. [웹 주소에서 가져오기]: 제목·본문 추출, 출처 주소·수집일 자동 기재, 내부망 주소 차단, robots.txt 준수, 2MB·3만 자 제한 10-14 로컬 시험 T28~T30 통과(입력 양식이 겹쳐 새로고침되던 오류를 고친 뒤).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">로그인이 필요하거나 자바스크립트로 그려지는 사이트는 못 읽을 수 있음.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">단계별 기사 작성 프로세스</t>
+  </si>
+  <si>
+    <t xml:space="preserve">핵심기술: 단계별 기사 작성 프로세스</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🟢</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CMS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">워크플로우 자체가 강점</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">I-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기자용 내부 B2B 적합성</t>
+  </si>
+  <si>
+    <t xml:space="preserve">설계 자체가 부합</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I-6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">윤리·저작권 대응(AI 출처관리)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제약: 윤리 및 저작권</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI 초안을 본문에 넣으면 기사 이력에 "AI 초안 반영" 자동 기록. 출고 창 AI 사용 안내, 웹 자료 출처·수집일, AI 이미지 출처·캡션 자동 표기</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">표기 문구와 기준은 회사 정책 확정 필요</t>
     </r>
     <r>
       <rPr>
@@ -789,38 +3671,220 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">바꾸면 이 시트의 개수가 자동으로 바뀝니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">노란색 칸</t>
-    </r>
-    <r>
-      <rPr>
+      <t xml:space="preserve">문장 단위 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">표시는 만들지 않음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(I-7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이 대신 근거 확인을 제공</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">).</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">I-7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">정확성·신뢰성(근거검증)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제약: 정보의 정확성·신뢰성</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI 초안 문장마다 내가 준 자료(답변·취재 메모·수집 팩트)와 글자 비교: 초록=근거 있음, 노랑=근거 못 찾음(숫자 불일치 포함). 끄고 켤 수 있음. 비어 있는 항목은 [확인 필요]로 표시</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10-19 배포 사이트에서 T20 통과: 근거 없는 "시장 환영 발언" 요청을 반영하지 않고 "근거가 없어 넣지 않았습니다"라고 답함. 근거 표시(초록/노랑)는 참고용이며 사실 확인을 대신하지 못함. 남은 작은 문제: "수집된 팩트 조각"의 발언 칸이 빈 따옴표로 보임.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I-8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">보안·프라이버시</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제약: 보안 및 프라이버시</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">RLS/RPC/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">권한감사 구현</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이번에 개인 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">키</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">구글 클라우드 키를 서버에서 암호화 저장하도록 강화</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">키는 로그</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">주소</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">채팅에 남기지 않음</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">J. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이번 작업에서 추가한 기능 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
         <sz val="10"/>
         <rFont val="Malgun Gothic"/>
         <family val="0"/>
@@ -830,14 +3894,16 @@
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">확인 필요 사항</t>
-    </r>
-    <r>
-      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">첨부표에 없던 항목</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
         <sz val="10"/>
         <rFont val="Malgun Gothic"/>
         <family val="0"/>
@@ -845,58 +3911,42 @@
       </rPr>
       <t xml:space="preserve">)</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">은 사람이 직접 확인해야 하는 내용입니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">확인 후 상태를 갱신해 주세요</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3. "🧪 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">구현</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">개인 AI 키 서버 암호화 저장</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">키를 계정별로 암호화해 서버에 저장(AES-GCM). 다른 컴퓨터에서도 재입력 불필요, 화면에는 뒤 4자리만 표시. 등록·AI 검수·받아쓰기 동작 확인. 구글 클라우드 키 칸에 엉뚱한 JSON을 넣으면 거절됨(확인)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기존 브라우저 저장 키는 자동으로 계정으로 옮겨짐.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">공급자</t>
     </r>
     <r>
       <rPr>
@@ -913,86 +3963,148 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">시험전</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">은 첨부표의 범례에 없던 새 표시입니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">코드를 완성했지만 실제 서비스에서 시험하지 않았다는 뜻입니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4. [</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">작업지시서 매핑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">시트는 동아일보 부트캠프 작업지시서의 필수 기능</t>
+      <t xml:space="preserve">모델 선택</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">제약: 반복적 모델 개선</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Gemini / OpenAI / Claude / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">사내 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">API </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">중 선택</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">모델은 목록에서 선택</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. 10-14 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">목록 최신화</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기본값 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Gemini gemini-3.8-flash, OpenAI gpt-6-luna, Claude claude-sonnet-5-5)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">10-16 시험은 gemini-3.6-flash로 진행(3.8은 구글 혼잡 503). 새 모델 이름 중 실제 호출 확인: gemini-3.8-flash·3.6-flash·3.5-flash-lite. 나머지는 시험 전. OpenAI gpt-6-luna(사진 분석)·gpt-image-2.5-flare 실제 호출 확인(10-16).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-3</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">혼잡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(503) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">자동 재시도</t>
     </r>
     <r>
       <rPr>
@@ -1009,7 +4121,59 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">핵심 기술</t>
+      <t xml:space="preserve">안내</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">일시 혼잡 시 자동으로 두 번 재시도, 계속되면 친절한 안내. 사용자가 재배포 후 정상 동작 확인함</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">녹음 받아쓰기 세부 옵션</t>
+  </si>
+  <si>
+    <t xml:space="preserve">핵심기술: STT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">언어 선택, 발표/인터뷰, 말하는 사람 수 힌트, 화자 이름 바꾸기(김기자·박시장으로 바꾸면 메모 전체에 반영). Gemini로 실사용 확인 완료. 한도: Gemini·OpenAI 10MB, 구글 클라우드 30분·60MB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">일본어·중국어와 사람 수 힌트는 직접 시험하지 못함.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">구글 클라우드 연동(받아쓰기 전용)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">서비스 계정 키(JSON)를 환경설정에 등록 → 서버가 구글 로그인 후 Speech-to-Text V2(Chirp 3)로 55초 조각 단위 받아쓰기. 인터뷰는 화자 구분 사용. 키 칸·잘못된 키 거절은 화면에서 확인</t>
+  </si>
+  <si>
+    <t xml:space="preserve">실제 구글 계정으로 받아쓰기를 호출해 본 적이 없습니다(T42·T43·T46·T47). 지역은 미국(us) 기본. 조각마다 화자 번호가 다시 매겨질 수 있음. 10-16 사용자 결정: 구글 클라우드·OpenAI 받아쓰기 시험은 보류.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-6</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">사용 현황 기록</t>
     </r>
     <r>
       <rPr>
@@ -1026,10 +4190,263 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">제약사항</t>
-    </r>
-    <r>
-      <rPr>
+      <t xml:space="preserve">표</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">제약/산출물: 성능·평가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">모든 AI 호출의 성공 여부·응답 시간·결과 길이를 기능·모델별로 기록(글 내용·이름은 기록 안 함). 환경설정 하단 표에서 "녹음 변환 · Gemini gemini-3.8-flash · 3회 · 성공률 100% · 평균 29초" 확인</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10-16 AI 초안·원자료 정리·사진 분석의 호출 기록이 빠져 있던 것을 고치고 재배포 후 기록되는 것 확인. 성능/평가 산출물용 수치는 이제부터 쌓임. OpenAI 받아쓰기와 이미지가 실제와 다른 모델 이름(whisper-1, 글쓰기 모델)으로 기록되던 것도 고침(재배포 후 확인).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">사용자 가이드 "API 연결 &amp; 요금" 탭</t>
+  </si>
+  <si>
+    <t xml:space="preserve">산출물/사용 안내</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Gemini·OpenAI·Claude·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">구글 클라우드 키 발급 순서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">연결 가능 기능 비교표</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">요금 표</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(2026-10-08 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기준</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">). </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">화면에서 탭 표시 확인</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">요금은 자주 바뀌므로 정기 갱신 필요. 모바일 폭 표시는 미확인.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">요구사항 분석표·테스트 데이터셋</t>
+  </si>
+  <si>
+    <t xml:space="preserve">산출물: 요구사항 분석표, 테스트 데이터셋</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엑셀 1개(요구사항 14건, 테스트 48건)와 샘플 자료 5개(docs/test-data). 10-16 시험 결과 반영</t>
+  </si>
+  <si>
+    <t xml:space="preserve">판정은 10-08·10-14 시험분만 기입. 나머지는 시험 후 기입.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">코드·파일 정리</t>
+  </si>
+  <si>
+    <t xml:space="preserve">사용하지 않는 코드(App.tsx의 죽은 코드 등) 삭제, README 갱신</t>
+  </si>
+  <si>
+    <t xml:space="preserve">별점 기능 파일 3개와 MediaLibraryDrawer.tsx는 폴더에 없음(10-16 확인). 남은 정리(안 쓰는 코드·중복 코드)는 재시험 뒤 진행 예정.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">별점·점수 평가 기록</t>
+  </si>
+  <si>
+    <t xml:space="preserve">작업지시서 ④ 보조</t>
+  </si>
+  <si>
+    <t xml:space="preserve">팀 결정으로 만들지 않기로 함(피드백→재생성 루프는 수정 지시·문단 재작성으로 충족)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">성능/평가 산출물은 N-6 사용 현황 표로 대신.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-11</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">OpenAI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">받아쓰기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">화자 구분 모델 포함</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">엔진에서 OpenAI 선택. 인터뷰는 화자 구분 전용 모델(gpt-4o-transcribe-diarize), 그 밖에 gpt-4o-transcribe·gpt-transcribe 등 선택 가능. 화자를 나누지 못하는 모델은 화면에 "화자 구분 불가" 표시</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10-16 OpenAI 키로 시험: 발표(gpt-4o-transcribe)는 한국어로 받아 적음(정확도는 Gemini보다 낮음, "심야버스"→"신약어스"). 인터뷰(gpt-4o-transcribe-diarize)는 화자는 나누지만 한국어 녹음을 영어로 잘못 적음 — 언어를 알려 주도록 고친 뒤에도 같아 모델 한계로 판단. 화면의 모델 설명에 "한국어 인터뷰는 Gemini 권장" 안내 추가.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">설정 화면 보안 문구 정정</t>
+  </si>
+  <si>
+    <t xml:space="preserve">설정 화면 윗부분에 "키는 브라우저에만 저장, 서버에는 저장 안 함"이라는 옛 문구가 남아 있어 현재 방식(서버에 암호화 저장)에 맞게 고침</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화면 반영은 개발 서버 새로고침 후 확인.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">시험용 합성 음성 자료</t>
+  </si>
+  <si>
+    <t xml:space="preserve">산출물: 테스트 데이터셋</t>
+  </si>
+  <si>
+    <t xml:space="preserve">한국어 인터뷰(두 사람)·한국어 발표·영어 발표 음성 3개(docs/test-data/audio_*.ogg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">사람 목소리 녹음으로 한 번 더 시험 권장. public/_tmp_test_audio는 재시험용으로 남겨 둠(GitHub에는 안 올라감).</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">K. 10-12 ~ 10-16 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">추가</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
         <sz val="10"/>
         <rFont val="Malgun Gothic"/>
         <family val="0"/>
@@ -1039,3425 +4456,8 @@
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">산출물이 통합표의 어느 항목에 해당하는지 보여 줍니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">번호</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기능</t>
-  </si>
-  <si>
-    <t xml:space="preserve">작업지시서 매핑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">첨부표 상태(이전)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">현재 상태</t>
-  </si>
-  <si>
-    <t xml:space="preserve">현재 상황 / 비고</t>
-  </si>
-  <si>
-    <t xml:space="preserve">확인 필요 사항</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
         <b val="true"/>
         <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A. </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기사 작성</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">편집 코어</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기사 작성·편집</t>
-  </si>
-  <si>
-    <t xml:space="preserve">✅</t>
-  </si>
-  <si>
-    <t xml:space="preserve">제목·부제목·본문 작성·저장</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">연속형 본문 편집기</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🟡</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화면 확인(2026-10-08): 제목·부제목·분류·본문이 한 장의 흰 문서 안에 이어서 보임</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">본문 미디어 삽입</t>
-  </si>
-  <si>
-    <t xml:space="preserve">이미지 캡션·크레딧·자르기, 본문 사이 끌어놓기 삽입이 코드에 있음</t>
-  </si>
-  <si>
-    <t xml:space="preserve">사진이 들어간 기사로 한 번 눈으로 확인 권장.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미디어 드래그 앤 드롭</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🔴</t>
-  </si>
-  <si>
-    <t xml:space="preserve">사진을 끌어다 놓는 처리(드래그 앤 드롭)가 코드에 다시 들어 있음 (BodyEditor)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화면에서 직접 끌어 놓아 보는 시험은 아직 안 했습니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기사 자동저장</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">article_blocks </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기반</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B. </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">워크플로우</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">출고</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">권한</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기사 상태 관리</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">🔴(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">오류발생</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">검토 요청 · 수정 요청 · 승인 · 출고 단계가 서버 기능으로 모두 있고, 편집기에서 상태를 바꿀 수 있음. 해결되었다는 보고 반영</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"오류발생" 원인은 표에 적혀 있지 않아, 해결 여부는 화면 시험으로 한 번 더 확인 권장.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">출고대기 자동 노출</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">출고 대기 기사는 공유 설정과 무관하게 부장 이상</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">부장 직급 또는 편집국장 역할</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">의 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">출고 대기 검토</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">에만 표시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(10-12 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">팀 결정으로 범위를 좁힘</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">10-16 사용자가 차장 계정으로 "출고 대기 검토"가 보이지 않음을 확인. 제한은 화면 목록 기준(서버 규칙은 그대로).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기사 공유 범위 설정</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미공개/같은 부서/전체</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공유와 출고검토 분리</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미공개라도 출고 대기면 부장 이상이 검토 가능</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">부서 기반 데스크 검토</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">🟡(↑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개선</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">서버가 같은 부서 데스크만 수정요청</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">승인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">배정을 허용</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">규칙을 문서로 정리함 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(docs/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">부서별</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">권한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">정책</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.md)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">다른 부서 대리 승인, 차장 최종 출고, 편집국장 전체 열람 여부는 팀이 정해야 함. 출고 대기 검토는 10-12부터 부장 이상만 보임(7번).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">사용자·직급별 권한</t>
-  </si>
-  <si>
-    <t xml:space="preserve">수습·평기자·차장·부장 구조</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">최종 출고 권한</t>
-  </si>
-  <si>
-    <t xml:space="preserve">부장 권한 기준</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C. AI </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">검수</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(Review) — </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기존 구현</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">13</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기사 검수</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">review-article-content. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">이제 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Gemini</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">뿐 아니라 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">OpenAI·Claude·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">사내 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">API </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">중 내가 고른 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">로 동작 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10-12 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">검수 지침 보강</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">주어 누락</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">제목에만 있는 내용</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">영문 표기 한글 우선</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">해외 대학</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기관 앞 국가명</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">보강분은 서버 함수 재배포 후 예문 시험 전. 공급자별 실사용도 시험 전(Gemini는 사용 확인됨).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">비문 검수</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">주술호응·성분누락·조사·시제 등 (10-12 주어 누락 지적 보강)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">검수 상세 설명</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">원문·유형·이유·확인사항·수정예시</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">제목-본문 정합성 검사</t>
-  </si>
-  <si>
-    <t xml:space="preserve">인물·기관·수치·주장 불일치 검수 (10-12 제목에만 있는 내용 지적 보강)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기사 표기법 검수</t>
-  </si>
-  <si>
-    <t xml:space="preserve">외래어·숫자·날짜·단위 등 (10-12 영문 표기 한글 우선·해외 기관 앞 국가명 규칙 추가)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PRESS-CMS </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기사 가이드</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">별도 문서 완비(표기 가이드 v1.1: 10-12 해외 대학·기관 앞 국가명 항목 추가)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원문 자동수정 방지</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">임의 원문 변경 금지 원칙 유지</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">D. AI </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">초안 생성 — 작업지시서 대응</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">D-1</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기사 초안 작성</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">작업지시서 ①</t>
-  </si>
-  <si>
-    <t xml:space="preserve">질문형 인터뷰(AI Interview Draft): ai-interview-draft + AiInterviewDraftPanel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">로우데이터 요약·정리</t>
-  </si>
-  <si>
-    <t xml:space="preserve">작업지시서 ②</t>
-  </si>
-  <si>
-    <t xml:space="preserve">취재메모/보도자료 → 5W1H·인용구·수치 구조화. 이번에 TXT·CSV·MD 파일 불러오기, 정리 전으로 되돌리기, 원자료에 없는 발언·숫자 걸러내기 추가</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10-16 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">로컬 시험 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">T07~T15 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">모두 통과</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(gemini-3.5-flash-lite): </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">숫자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">발언 원문 그대로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">문서 속 지시문 무시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">엇갈린 숫자 확인 필요로 분리</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">한글 엑셀 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CSV </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">읽기</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, 3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">만 자 초과 안내</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">D-3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">대화형(Chat) 프롬프트</t>
-  </si>
-  <si>
-    <t xml:space="preserve">작업지시서 ③</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">질문</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기자 답변 채팅 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">UI</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">D-4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">피드백→재생성 루프</t>
-  </si>
-  <si>
-    <t xml:space="preserve">작업지시서 ④</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">regenerate_section </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">모드로 섹션별 재작성 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">전체 수정 지시</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">T16~T19·T21 통과. T19는 10-16 문단 순서가 바뀌는 오류를 고친 뒤 재시험 통과(고른 문단만 바뀌고 리드·다른 문단 그대로). 별점·점수 기록은 만들지 않기로 결정(N-10).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">제목 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개 추천</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">✅(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">통합</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">독립 기능 대신 인터뷰 finalize 결과에 제목 후보 2~3개로 통합 구현 (통합 구현)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D-5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">톤·스타일·키워드 기반 작성</t>
-  </si>
-  <si>
-    <t xml:space="preserve">작업지시서 핵심기술(프롬프트)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기사 어조 선택(스트레이트/해설·분석/인터뷰/피처)이 화면에 있고 서버가 어조별 지시문을 적용함</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10-16 T03 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">통과</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">해설 톤</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">배경</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">맥락이 늘고 사실 동일</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">). </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">인터뷰 톤으로 다시 만들기는 화면 변화가 확인되지 않음</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">D-6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">본문 반영 안전성</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI 초안 [본문 삽입]은 편집기에 직접 넣고 바로 저장(10-14 본문에 안 들어가던 오류 수정, 로컬 확인). 직접 INSERT 미사용</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D-7</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">모델 라우팅 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">번째 슬롯</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ai_system_settings.article_generation_model(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">팀 기본값</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">). 10-16</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">부터 실제 호출은 사람마다 저장한 기능별 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI(N-23)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">를 따름</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">SQL 20261014100000 실행 완료.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">E. </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">협업 피드백</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">드래그형 기사 피드백</t>
-  </si>
-  <si>
-    <t xml:space="preserve">본문 글자를 드래그해 선택하면 피드백 입력창이 열리고 선택한 문장이 함께 저장됨 (코드 확인)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">피드백 형광펜 표시</t>
-  </si>
-  <si>
-    <t xml:space="preserve">피드백이 달린 문장을 형광펜으로 표시 (feedbackHighlight)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">피드백 위치 바로가기</t>
-  </si>
-  <si>
-    <t xml:space="preserve">피드백을 누르면 본문의 해당 위치로 부드럽게 이동. 위치를 못 찾으면 "원문 위치를 찾을 수 없음" 표시</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">피드백 위치 복구</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🔵</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">본문이 조금 바뀌어도 앞뒤 문맥과 선택 문장으로 위치를 다시 찾는 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">단계 복구가 들어 있음 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(DB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">에도 문맥 칸 추가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">본문을 크게 고친 뒤 실제로 위치가 따라오는지는 시험 전.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">F. </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">이력</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">분류</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기사 분류</t>
-  </si>
-  <si>
-    <t xml:space="preserve">정치·경제·사회 등</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">해시태그</t>
-  </si>
-  <si>
-    <t xml:space="preserve">추가·삭제 UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기사 이력 관리</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">History </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">영역</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">G. </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">조직</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/HR</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">28</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HR </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">프로필 설정 복구</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">인사 담당자는 환경설정에서 AI·미디어 메뉴를 빼고 내 프로필만 보이게 정리. 라벨도 인사 관리자용으로 변경</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HR 계정으로 로그인해 확인 필요. 10-14 인사부 전용 왼쪽 메뉴와 사용법 안내 버튼 추가(N-19).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HR </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">직원 명부</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">보안 RPC 구현 완료</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HR </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">직원정보 수정</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">직원 명부의 [수정] 버튼: 부서·직책·직급·시스템 역할을 바꿈 (본인 계정은 제외). 바꾸면 변경 기록에 남고 본인에게 알림</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10-16 사용자가 인사부 계정으로 동작 확인.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">직원 계정 비활성화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">직원 명부의 [비활성화]/[다시 사용] 버튼: 로그인 차단 + 접속 중인 세션 종료. 기사·기록은 그대로 보존. 로그인 화면에 "비활성화된 계정입니다" 안내</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10-16 사용자가 인사부 계정으로 동작 확인. 이미 열린 화면은 최대 1시간 안에 끊길 수 있음.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">회원가입 승인 관리</t>
-  </si>
-  <si>
-    <t xml:space="preserve">가입 신청 즉시 승인 대기 계정 생성 + 임시 비밀번호(한 번만 표시). 인사부 승인 시 부서·직책·직급·역할 반영, 반려 시 사용 중지(10-12 변경, N-14·N-15)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10-16 사용자가 새 가입 신청 흐름을 확인.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">H. </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">알림</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">감사</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">통합 알림센터</t>
-  </si>
-  <si>
-    <t xml:space="preserve">상단 🔔 알림센터 구현. 모든 화면에서 열람, 읽음·모두 읽음 처리</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HR </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">가입승인 알림</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">누가 가입을 신청하면 인사 담당자 전원에게 "가입 승인 요청" 알림. 누르면 가입 승인 메뉴로 이동. 인사 포털 상단에도 🔔 표시</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQL 실행 후 시험 필요.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기사 피드백 알림</t>
-  </si>
-  <si>
-    <t xml:space="preserve">수정 요청 알림 + 새 피드백 알림 구현. 2026-10-08 사용자가 실제 알림 도착 확인</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">출고대기 알림</t>
-  </si>
-  <si>
-    <t xml:space="preserve">검토 요청·재검토 요청·승인 완료·출고 완료 알림 있음</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">인사정보 변경 알림</t>
-  </si>
-  <si>
-    <t xml:space="preserve">인사 담당자가 내 부서·직책·직급·역할 등을 바꾸면 본인에게 "인사 정보 변경" 알림 (바뀐 내용 포함)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">알림 업무 바로가기</t>
-  </si>
-  <si>
-    <t xml:space="preserve">알림을 누르면 해당 기사로 바로 이동</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">알림 영구저장·Realtime</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">알림이 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">에 영구 저장되고 새 알림이 오면 바로 🔔에 반영</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(Realtime). </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">사용자가 정상 동작 확인</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Realtime이 끊겨도 60초마다 다시 확인.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">감사 로그</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기사 감사 기록 8종 + 인사·권한 변경 기록(직원 정보·부서·직책 변경 시 자동 기록, 인사 포털 "인사·권한 변경 기록" 메뉴)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">마이그레이션 20261008210000 실행 후 확인 필요.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">상단 헤더 단순화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">상단 헤더에 검색·알림센터·내 프로필 중심으로 정리됨 (코드 확인)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화면 모양은 직접 확인 권장.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">I. </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">인프라 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">· </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">작업지시서 전용 항목</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">42</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Supabase </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">데이터 연동</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Auth/Postgres/Storage/Edge Functions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I-1</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">STT(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">음성→텍스트</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">핵심기술: 음성 데이터의 텍스트 변환</t>
-  </si>
-  <si>
-    <t xml:space="preserve">구현·실사용 확인(Gemini). [녹음 받아쓰기]: 언어 4개, 발표·강연/인터뷰(화자 구분), 화자 이름 바꾸기, 엔진 3종(Gemini·OpenAI·구글 클라우드). 2026-10-08 합성 음성으로 인터뷰(화자1·2 분리)·발표(화자 표시 없음)·영어(번역 없이 영어 그대로) 모두 통과. Claude는 소리를 들을 수 없어 제외 10-14 받아쓰기 모델을 글쓰기 모델과 따로 고르도록 분리(N-18).</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10-16 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">로컬 재시험 통과</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(Gemini gemini-3.8-flash·gemini-3.6-flash, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">발표</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">인터뷰 모두</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">). 3.8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">은 첫 시도 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회 빈 결과</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">("</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">받아 적을 말을 찾지 못했습니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">") </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">후 재시도에서 정상 — 가끔 다시 눌러야 할 수 있음</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. gemini-3.5-transcribe</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">는 실패해 목록에서 뺌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. OpenAI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">는 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10-16 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">시험</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(N-11 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">참고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">구글 클라우드는 사용자 결정으로 보류</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">조직 정책으로 키 생성이 막힘</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">). </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">받아쓴 지명</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">숫자는 반드시 확인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">합성 음성의 시 이름이 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">당진</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">"/"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">하나시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">로 다르게 적힘</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">).</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">I-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">이미지 생성 AI API</t>
-  </si>
-  <si>
-    <t xml:space="preserve">핵심기술: 이미지 생성 AI API</t>
-  </si>
-  <si>
-    <t xml:space="preserve">구현됨. 미디어 탭 [AI 이미지]: 설명글→생성→미리보기→라이브러리 업로드. 출처 "AI 생성(모델명)"과 캡션 [AI 생성 이미지] 자동 표기. Gemini·OpenAI 지원</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10-16 OpenAI 키로 시험 통과(T33): gpt-image-2.5-flare로 생성, 올리면 캡션 [AI 생성 이미지]·출처 "AI 생성 (OpenAI gpt-image-2.5-flare)" 자동 표기. T34: 실제 로고가 그려지는 문제를 발견해, 로고·상표·실존 인물 얼굴 요청은 AI 호출 전에 거절하도록 고친 뒤 통과. Gemini 이미지 모델은 결제 연결 키가 없어 시험 못 함. OpenAI 이미지는 요금이 높으니 주의.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I-3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">웹크롤링·데이터 처리</t>
-  </si>
-  <si>
-    <t xml:space="preserve">핵심기술: 웹 크롤링 및 데이터 처리</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🟠</t>
-  </si>
-  <si>
-    <t xml:space="preserve">구현됨. [웹 주소에서 가져오기]: 제목·본문 추출, 출처 주소·수집일 자동 기재, 내부망 주소 차단, robots.txt 준수, 2MB·3만 자 제한 10-14 로컬 시험 T28~T30 통과(입력 양식이 겹쳐 새로고침되던 오류를 고친 뒤).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">로그인이 필요하거나 자바스크립트로 그려지는 사이트는 못 읽을 수 있음.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I-4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">단계별 기사 작성 프로세스</t>
-  </si>
-  <si>
-    <t xml:space="preserve">핵심기술: 단계별 기사 작성 프로세스</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🟢</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CMS </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">워크플로우 자체가 강점</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">I-5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기자용 내부 B2B 적합성</t>
-  </si>
-  <si>
-    <t xml:space="preserve">설계 자체가 부합</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I-6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">윤리·저작권 대응(AI 출처관리)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">제약: 윤리 및 저작권</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI 초안을 본문에 넣으면 기사 이력에 "AI 초안 반영" 자동 기록. 출고 창 AI 사용 안내, 웹 자료 출처·수집일, AI 이미지 출처·캡션 자동 표기</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">표기 문구와 기준은 회사 정책 확정 필요</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">문장 단위 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">표시는 만들지 않음</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(I-7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">이 대신 근거 확인을 제공</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">).</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">I-7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">정확성·신뢰성(근거검증)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">제약: 정보의 정확성·신뢰성</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI 초안 문장마다 내가 준 자료(답변·취재 메모·수집 팩트)와 글자 비교: 초록=근거 있음, 노랑=근거 못 찾음(숫자 불일치 포함). 끄고 켤 수 있음. 비어 있는 항목은 [확인 필요]로 표시</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T20 대응(10-16): 수정 지시로 자료에 없는 발언·사실을 넣어 달라고 하면 넣지 않고 "근거가 없어 넣지 않았습니다"라고 답하도록 지시문 변경 + 서버에서 수정 지시가 수집된 사실(육하원칙·발언·수치)을 바꾸지 못하게 막음. ai-interview-draft 재배포 후 재시험 필요. 그 밖: 10-16 T02에서 "수집된 팩트 조각"의 발언 칸이 빈 따옴표로 표시되는 문제 발견(본문 인용은 정상).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I-8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">보안·프라이버시</t>
-  </si>
-  <si>
-    <t xml:space="preserve">제약: 보안 및 프라이버시</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">RLS/RPC/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">권한감사 구현</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">이번에 개인 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">키</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">구글 클라우드 키를 서버에서 암호화 저장하도록 강화</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">키는 로그</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">주소</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">채팅에 남기지 않음</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">J. </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">이번 작업에서 추가한 기능 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">첨부표에 없던 항목</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">N-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">개인 AI 키 서버 암호화 저장</t>
-  </si>
-  <si>
-    <t xml:space="preserve">—</t>
-  </si>
-  <si>
-    <t xml:space="preserve">키를 계정별로 암호화해 서버에 저장(AES-GCM). 다른 컴퓨터에서도 재입력 불필요, 화면에는 뒤 4자리만 표시. 등록·AI 검수·받아쓰기 동작 확인. 구글 클라우드 키 칸에 엉뚱한 JSON을 넣으면 거절됨(확인)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기존 브라우저 저장 키는 자동으로 계정으로 옮겨짐.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-2</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">공급자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">모델 선택</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">제약: 반복적 모델 개선</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Gemini / OpenAI / Claude / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">사내 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">API </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">중 선택</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">모델은 목록에서 선택</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. 10-14 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">목록 최신화</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기본값 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Gemini gemini-3.8-flash, OpenAI gpt-6-luna, Claude claude-sonnet-5-5)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">10-16 시험은 gemini-3.6-flash로 진행(3.8은 구글 혼잡 503). 새 모델 이름 중 실제 호출 확인: gemini-3.8-flash·3.6-flash·3.5-flash-lite. 나머지는 시험 전. OpenAI gpt-6-luna(사진 분석)·gpt-image-2.5-flare 실제 호출 확인(10-16).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-3</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">혼잡</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(503) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">자동 재시도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">안내</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">일시 혼잡 시 자동으로 두 번 재시도, 계속되면 친절한 안내. 사용자가 재배포 후 정상 동작 확인함</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">녹음 받아쓰기 세부 옵션</t>
-  </si>
-  <si>
-    <t xml:space="preserve">핵심기술: STT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">언어 선택, 발표/인터뷰, 말하는 사람 수 힌트, 화자 이름 바꾸기(김기자·박시장으로 바꾸면 메모 전체에 반영). Gemini로 실사용 확인 완료. 한도: Gemini·OpenAI 10MB, 구글 클라우드 30분·60MB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">일본어·중국어와 사람 수 힌트는 직접 시험하지 못함.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">구글 클라우드 연동(받아쓰기 전용)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">서비스 계정 키(JSON)를 환경설정에 등록 → 서버가 구글 로그인 후 Speech-to-Text V2(Chirp 3)로 55초 조각 단위 받아쓰기. 인터뷰는 화자 구분 사용. 키 칸·잘못된 키 거절은 화면에서 확인</t>
-  </si>
-  <si>
-    <t xml:space="preserve">실제 구글 계정으로 받아쓰기를 호출해 본 적이 없습니다(T42·T43·T46·T47). 지역은 미국(us) 기본. 조각마다 화자 번호가 다시 매겨질 수 있음. 10-16 사용자 결정: 구글 클라우드·OpenAI 받아쓰기 시험은 보류.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-6</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">사용 현황 기록</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">표</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">제약/산출물: 성능·평가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">모든 AI 호출의 성공 여부·응답 시간·결과 길이를 기능·모델별로 기록(글 내용·이름은 기록 안 함). 환경설정 하단 표에서 "녹음 변환 · Gemini gemini-3.8-flash · 3회 · 성공률 100% · 평균 29초" 확인</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10-16 AI 초안·원자료 정리·사진 분석의 호출 기록이 빠져 있던 것을 고치고 재배포 후 기록되는 것 확인. 성능/평가 산출물용 수치는 이제부터 쌓임. OpenAI 받아쓰기와 이미지가 실제와 다른 모델 이름(whisper-1, 글쓰기 모델)으로 기록되던 것도 고침(재배포 후 확인).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">사용자 가이드 "API 연결 &amp; 요금" 탭</t>
-  </si>
-  <si>
-    <t xml:space="preserve">산출물/사용 안내</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Gemini·OpenAI·Claude·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">구글 클라우드 키 발급 순서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">연결 가능 기능 비교표</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">요금 표</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(2026-10-08 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기준</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">). </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">화면에서 탭 표시 확인</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">요금은 자주 바뀌므로 정기 갱신 필요. 모바일 폭 표시는 미확인.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">요구사항 분석표·테스트 데이터셋</t>
-  </si>
-  <si>
-    <t xml:space="preserve">산출물: 요구사항 분석표, 테스트 데이터셋</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엑셀 1개(요구사항 14건, 테스트 48건)와 샘플 자료 5개(docs/test-data). 10-16 시험 결과 반영</t>
-  </si>
-  <si>
-    <t xml:space="preserve">판정은 10-08·10-14 시험분만 기입. 나머지는 시험 후 기입.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">코드·파일 정리</t>
-  </si>
-  <si>
-    <t xml:space="preserve">사용하지 않는 코드(App.tsx의 죽은 코드 등) 삭제, README 갱신</t>
-  </si>
-  <si>
-    <t xml:space="preserve">별점 기능 파일 3개와 MediaLibraryDrawer.tsx는 폴더에 없음(10-16 확인). 남은 정리(안 쓰는 코드·중복 코드)는 재시험 뒤 진행 예정.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">별점·점수 평가 기록</t>
-  </si>
-  <si>
-    <t xml:space="preserve">작업지시서 ④ 보조</t>
-  </si>
-  <si>
-    <t xml:space="preserve">팀 결정으로 만들지 않기로 함(피드백→재생성 루프는 수정 지시·문단 재작성으로 충족)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">성능/평가 산출물은 N-6 사용 현황 표로 대신.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-11</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">OpenAI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">받아쓰기</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">화자 구분 모델 포함</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">엔진에서 OpenAI 선택. 인터뷰는 화자 구분 전용 모델(gpt-4o-transcribe-diarize), 그 밖에 gpt-4o-transcribe·gpt-transcribe 등 선택 가능. 화자를 나누지 못하는 모델은 화면에 "화자 구분 불가" 표시</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10-16 OpenAI 키로 시험: 발표(gpt-4o-transcribe)는 한국어로 받아 적음(정확도는 Gemini보다 낮음, "심야버스"→"신약어스"). 인터뷰(gpt-4o-transcribe-diarize)는 화자는 나누지만 한국어 녹음을 영어로 잘못 적음 — 언어를 알려 주도록 고친 뒤에도 같아 모델 한계로 판단. 화면의 모델 설명에 "한국어 인터뷰는 Gemini 권장" 안내 추가.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">설정 화면 보안 문구 정정</t>
-  </si>
-  <si>
-    <t xml:space="preserve">설정 화면 윗부분에 "키는 브라우저에만 저장, 서버에는 저장 안 함"이라는 옛 문구가 남아 있어 현재 방식(서버에 암호화 저장)에 맞게 고침</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화면 반영은 개발 서버 새로고침 후 확인.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">시험용 합성 음성 자료</t>
-  </si>
-  <si>
-    <t xml:space="preserve">산출물: 테스트 데이터셋</t>
-  </si>
-  <si>
-    <t xml:space="preserve">한국어 인터뷰(두 사람)·한국어 발표·영어 발표 음성 3개(docs/test-data/audio_*.ogg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">사람 목소리 녹음으로 한 번 더 시험 권장. public/_tmp_test_audio는 재시험용으로 남겨 둠(GitHub에는 안 올라감).</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">K. 10-12 ~ 10-16 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">추가</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -4567,10 +4567,10 @@
     <t xml:space="preserve">배포(GitHub → Render)</t>
   </si>
   <si>
-    <t xml:space="preserve">배포 주소(a-team-press-cms.onrender.com)는 이전 완성본으로 운영 중. 10-16 SQL(20261014100000) 실행, 최신 수정분 GitHub 업로드 진행</t>
-  </si>
-  <si>
-    <t xml:space="preserve">업로드 후 Render 자동 배포와 Supabase 사이트 주소(Site URL) 등록 확인 필요.</t>
+    <t xml:space="preserve">10-19 GitHub 업로드 → Render 배포 확인(배포 사이트 파일에서 기능별 AI 칸·인사부 메뉴·KB 표시·모델 안내 문구 확인). 서버 함수도 모두 재배포</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10-19 배포 사이트에서 로그인·환경설정·AI 초안 수정 지시 동작 확인. 녹음 정리는 같은 서버 함수로 로컬에서 확인함.</t>
   </si>
   <si>
     <t xml:space="preserve">N-23</t>
@@ -5306,7 +5306,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="19">
+  <dxfs count="18">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -5374,14 +5374,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFE1BEE7"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFF59D"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -5733,7 +5725,7 @@
       </c>
       <c r="B5" s="6" t="n">
         <f aca="false">COUNTIF('통합 현황표'!$E$2:$E$92,A5)</f>
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>6</v>
@@ -5745,7 +5737,7 @@
       </c>
       <c r="B6" s="6" t="n">
         <f aca="false">COUNTIF('통합 현황표'!$E$2:$E$92,A6)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>8</v>
@@ -5805,7 +5797,7 @@
       </c>
       <c r="B11" s="6" t="n">
         <f aca="false">COUNTIF('통합 현황표'!$E$2:$E$92,A11)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>18</v>
@@ -7212,7 +7204,7 @@
         <v>243</v>
       </c>
       <c r="E66" s="23" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="F66" s="7" t="s">
         <v>262</v>
@@ -7753,7 +7745,7 @@
         <v>271</v>
       </c>
       <c r="E91" s="23" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F91" s="7" t="s">
         <v>363</v>
@@ -7801,28 +7793,28 @@
     <mergeCell ref="A82:G82"/>
   </mergeCells>
   <conditionalFormatting sqref="E2:E92">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>$E2="✅ 완료"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>$E2="🟡 보완중"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>$E2="🟠 추가정립필요"</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
       <formula>$E2="🔴 복구/긴급필요"</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
       <formula>$E2="🔵 구현예정"</formula>
     </cfRule>
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
       <formula>$E2="🟢 강점"</formula>
     </cfRule>
-    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
       <formula>$E2="🧪 구현·시험전"</formula>
     </cfRule>
-    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
+    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
       <formula>$E2="⚪ 하지 않기로 함"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8183,28 +8175,28 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D19">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>$D2="✅ 완료"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>$D2="🟡 보완중"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>$D2="🟠 추가정립필요"</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
       <formula>$D2="🔴 복구/긴급필요"</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
       <formula>$D2="🔵 구현예정"</formula>
     </cfRule>
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
       <formula>$D2="🟢 강점"</formula>
     </cfRule>
-    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
       <formula>$D2="🧪 구현·시험전"</formula>
     </cfRule>
-    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
+    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
       <formula>$D2="⚪ 하지 않기로 함"</formula>
     </cfRule>
   </conditionalFormatting>
